--- a/artfynd/A 19925-2025 artfynd.xlsx
+++ b/artfynd/A 19925-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125609255</v>
+        <v>125607813</v>
       </c>
       <c r="B2" t="n">
-        <v>101727</v>
+        <v>100451</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>22</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarptandad daggkåpa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alchemilla oxyodonta</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Buser) C. G. Westerl.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Nymansbodarna, Nymansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443499</v>
+        <v>443693</v>
       </c>
       <c r="R2" t="n">
-        <v>7023160</v>
+        <v>7022900</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På marken i dikeskant nära före detta fäbod</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -918,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125608291</v>
+        <v>125609255</v>
       </c>
       <c r="B4" t="n">
-        <v>75011</v>
+        <v>101727</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,38 +921,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>306</v>
+        <v>22</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Skarptandad daggkåpa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alchemilla oxyodonta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Buser) C. G. Westerl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nymansbodarna, Nymansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443422</v>
+        <v>443499</v>
       </c>
       <c r="R4" t="n">
-        <v>7022960</v>
+        <v>7023160</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På ved på gammal jordkällare</t>
+          <t>På marken i dikeskant nära före detta fäbod</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125607813</v>
+        <v>125608448</v>
       </c>
       <c r="B5" t="n">
-        <v>100451</v>
+        <v>77879</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,25 +1047,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>228579</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>443693</v>
+        <v>443422</v>
       </c>
       <c r="R5" t="n">
-        <v>7022900</v>
+        <v>7022960</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125608448</v>
+        <v>125608291</v>
       </c>
       <c r="B6" t="n">
-        <v>77879</v>
+        <v>75011</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,25 +1164,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228579</v>
+        <v>306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gammal gran i äldre granskog</t>
+          <t>På ved på gammal jordkällare</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 19925-2025 artfynd.xlsx
+++ b/artfynd/A 19925-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125607813</v>
+        <v>125608291</v>
       </c>
       <c r="B2" t="n">
-        <v>100451</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75052</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443693</v>
+        <v>443422</v>
       </c>
       <c r="R2" t="n">
-        <v>7022900</v>
+        <v>7022960</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På ved på gammal jordkällare</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,37 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125608427</v>
+        <v>125607813</v>
       </c>
       <c r="B3" t="n">
-        <v>75025</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443422</v>
+        <v>443693</v>
       </c>
       <c r="R3" t="n">
-        <v>7022960</v>
+        <v>7022900</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gran i äldre granskog</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +892,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -912,12 +902,7 @@
         <v>125609255</v>
       </c>
       <c r="B4" t="n">
-        <v>101727</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101782</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,15 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125608448</v>
+        <v>125608427</v>
       </c>
       <c r="B5" t="n">
-        <v>77879</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75066</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1110,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,12 +1100,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal gran i äldre granskog</t>
+          <t>På gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,44 +1125,39 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125608291</v>
+        <v>125608448</v>
       </c>
       <c r="B6" t="n">
-        <v>75011</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>77921</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>306</v>
+        <v>228579</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1227,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,12 +1212,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På ved på gammal jordkällare</t>
+          <t>På gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,7 +1237,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 19925-2025 artfynd.xlsx
+++ b/artfynd/A 19925-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>125607813</v>
       </c>
       <c r="B3" t="n">
-        <v>100506</v>
+        <v>100513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,61 +892,52 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125609255</v>
+        <v>125608427</v>
       </c>
       <c r="B4" t="n">
-        <v>101782</v>
+        <v>75066</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>22</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarptandad daggkåpa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alchemilla oxyodonta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Buser) C. G. Westerl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nymansbodarna, Nymansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443499</v>
+        <v>443422</v>
       </c>
       <c r="R4" t="n">
-        <v>7023160</v>
+        <v>7022960</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På marken i dikeskant nära före detta fäbod</t>
+          <t>På gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,52 +1004,61 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125608427</v>
+        <v>125609255</v>
       </c>
       <c r="B5" t="n">
-        <v>75066</v>
+        <v>101789</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>22</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skarptandad daggkåpa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alchemilla oxyodonta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Buser) C. G. Westerl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nymansbodarna, Nymansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>443422</v>
+        <v>443499</v>
       </c>
       <c r="R5" t="n">
-        <v>7022960</v>
+        <v>7023160</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gran i äldre granskog</t>
+          <t>På marken i dikeskant nära före detta fäbod</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 19925-2025 artfynd.xlsx
+++ b/artfynd/A 19925-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125608291</v>
+        <v>125607813</v>
       </c>
       <c r="B2" t="n">
-        <v>75052</v>
+        <v>100513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>306</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443422</v>
+        <v>443693</v>
       </c>
       <c r="R2" t="n">
-        <v>7022960</v>
+        <v>7022900</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På ved på gammal jordkällare</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125607813</v>
+        <v>125608291</v>
       </c>
       <c r="B3" t="n">
-        <v>100513</v>
+        <v>75052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443693</v>
+        <v>443422</v>
       </c>
       <c r="R3" t="n">
-        <v>7022900</v>
+        <v>7022960</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På ved på gammal jordkällare</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 19925-2025 artfynd.xlsx
+++ b/artfynd/A 19925-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125607813</v>
+        <v>125608291</v>
       </c>
       <c r="B2" t="n">
-        <v>100513</v>
+        <v>75053</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443693</v>
+        <v>443422</v>
       </c>
       <c r="R2" t="n">
-        <v>7022900</v>
+        <v>7022960</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På ved på gammal jordkällare</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125608291</v>
+        <v>125607813</v>
       </c>
       <c r="B3" t="n">
-        <v>75052</v>
+        <v>100516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>306</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443422</v>
+        <v>443693</v>
       </c>
       <c r="R3" t="n">
-        <v>7022960</v>
+        <v>7022900</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På ved på gammal jordkällare</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>125608427</v>
       </c>
       <c r="B4" t="n">
-        <v>75066</v>
+        <v>75067</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1014,7 +1014,7 @@
         <v>125609255</v>
       </c>
       <c r="B5" t="n">
-        <v>101789</v>
+        <v>101792</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>125608448</v>
       </c>
       <c r="B6" t="n">
-        <v>77921</v>
+        <v>77922</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 19925-2025 artfynd.xlsx
+++ b/artfynd/A 19925-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125608291</v>
+        <v>125607813</v>
       </c>
       <c r="B2" t="n">
-        <v>75053</v>
+        <v>100520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>306</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443422</v>
+        <v>443693</v>
       </c>
       <c r="R2" t="n">
-        <v>7022960</v>
+        <v>7022900</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På ved på gammal jordkällare</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125607813</v>
+        <v>125608291</v>
       </c>
       <c r="B3" t="n">
-        <v>100516</v>
+        <v>75053</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443693</v>
+        <v>443422</v>
       </c>
       <c r="R3" t="n">
-        <v>7022900</v>
+        <v>7022960</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På ved på gammal jordkällare</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,45 +899,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125608427</v>
+        <v>125609255</v>
       </c>
       <c r="B4" t="n">
-        <v>75067</v>
+        <v>101796</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>22</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skarptandad daggkåpa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alchemilla oxyodonta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Buser) C. G. Westerl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nymansbodarna, Nymansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443422</v>
+        <v>443499</v>
       </c>
       <c r="R4" t="n">
-        <v>7022960</v>
+        <v>7023160</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gran i äldre granskog</t>
+          <t>På marken i dikeskant nära före detta fäbod</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,54 +1020,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125609255</v>
+        <v>125608427</v>
       </c>
       <c r="B5" t="n">
-        <v>101792</v>
+        <v>75067</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>22</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarptandad daggkåpa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alchemilla oxyodonta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Buser) C. G. Westerl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nymansbodarna, Nymansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>443499</v>
+        <v>443422</v>
       </c>
       <c r="R5" t="n">
-        <v>7023160</v>
+        <v>7022960</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På marken i dikeskant nära före detta fäbod</t>
+          <t>På gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,7 +1135,7 @@
         <v>125608448</v>
       </c>
       <c r="B6" t="n">
-        <v>77922</v>
+        <v>77926</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 19925-2025 artfynd.xlsx
+++ b/artfynd/A 19925-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125607813</v>
+        <v>125608291</v>
       </c>
       <c r="B2" t="n">
-        <v>100520</v>
+        <v>75053</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443693</v>
+        <v>443422</v>
       </c>
       <c r="R2" t="n">
-        <v>7022900</v>
+        <v>7022960</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På ved på gammal jordkällare</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125608291</v>
+        <v>125607813</v>
       </c>
       <c r="B3" t="n">
-        <v>75053</v>
+        <v>100521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>306</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443422</v>
+        <v>443693</v>
       </c>
       <c r="R3" t="n">
-        <v>7022960</v>
+        <v>7022900</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På ved på gammal jordkällare</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,54 +899,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125609255</v>
+        <v>125608427</v>
       </c>
       <c r="B4" t="n">
-        <v>101796</v>
+        <v>75067</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>22</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarptandad daggkåpa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alchemilla oxyodonta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Buser) C. G. Westerl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nymansbodarna, Nymansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443499</v>
+        <v>443422</v>
       </c>
       <c r="R4" t="n">
-        <v>7023160</v>
+        <v>7022960</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På marken i dikeskant nära före detta fäbod</t>
+          <t>På gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,45 +1011,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125608427</v>
+        <v>125609255</v>
       </c>
       <c r="B5" t="n">
-        <v>75067</v>
+        <v>101797</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>22</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skarptandad daggkåpa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alchemilla oxyodonta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Buser) C. G. Westerl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nymansbodarna, Nymansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>443422</v>
+        <v>443499</v>
       </c>
       <c r="R5" t="n">
-        <v>7022960</v>
+        <v>7023160</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gran i äldre granskog</t>
+          <t>På marken i dikeskant nära före detta fäbod</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 19925-2025 artfynd.xlsx
+++ b/artfynd/A 19925-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125608291</v>
+        <v>125607813</v>
       </c>
       <c r="B2" t="n">
-        <v>75053</v>
+        <v>100523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>306</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443422</v>
+        <v>443693</v>
       </c>
       <c r="R2" t="n">
-        <v>7022960</v>
+        <v>7022900</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På ved på gammal jordkällare</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125607813</v>
+        <v>125608291</v>
       </c>
       <c r="B3" t="n">
-        <v>100521</v>
+        <v>75054</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443693</v>
+        <v>443422</v>
       </c>
       <c r="R3" t="n">
-        <v>7022900</v>
+        <v>7022960</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På ved på gammal jordkällare</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,45 +899,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125608427</v>
+        <v>125609255</v>
       </c>
       <c r="B4" t="n">
-        <v>75067</v>
+        <v>101799</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>22</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skarptandad daggkåpa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alchemilla oxyodonta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Buser) C. G. Westerl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nymansbodarna, Nymansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443422</v>
+        <v>443499</v>
       </c>
       <c r="R4" t="n">
-        <v>7022960</v>
+        <v>7023160</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gran i äldre granskog</t>
+          <t>På marken i dikeskant nära före detta fäbod</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,54 +1020,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125609255</v>
+        <v>125608427</v>
       </c>
       <c r="B5" t="n">
-        <v>101797</v>
+        <v>75068</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>22</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarptandad daggkåpa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alchemilla oxyodonta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Buser) C. G. Westerl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nymansbodarna, Nymansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>443499</v>
+        <v>443422</v>
       </c>
       <c r="R5" t="n">
-        <v>7023160</v>
+        <v>7022960</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På marken i dikeskant nära före detta fäbod</t>
+          <t>På gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1135,7 +1135,7 @@
         <v>125608448</v>
       </c>
       <c r="B6" t="n">
-        <v>77926</v>
+        <v>77927</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 19925-2025 artfynd.xlsx
+++ b/artfynd/A 19925-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125607813</v>
+        <v>125608291</v>
       </c>
       <c r="B2" t="n">
-        <v>100523</v>
+        <v>75054</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443693</v>
+        <v>443422</v>
       </c>
       <c r="R2" t="n">
-        <v>7022900</v>
+        <v>7022960</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På marken i äldre granskog</t>
+          <t>På ved på gammal jordkällare</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125608291</v>
+        <v>125607813</v>
       </c>
       <c r="B3" t="n">
-        <v>75054</v>
+        <v>100525</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>306</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443422</v>
+        <v>443693</v>
       </c>
       <c r="R3" t="n">
-        <v>7022960</v>
+        <v>7022900</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På ved på gammal jordkällare</t>
+          <t>På marken i äldre granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,54 +899,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125609255</v>
+        <v>125608427</v>
       </c>
       <c r="B4" t="n">
-        <v>101799</v>
+        <v>75068</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>22</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarptandad daggkåpa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alchemilla oxyodonta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Buser) C. G. Westerl.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nymansbodarna, Nymansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443499</v>
+        <v>443422</v>
       </c>
       <c r="R4" t="n">
-        <v>7023160</v>
+        <v>7022960</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På marken i dikeskant nära före detta fäbod</t>
+          <t>På gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,45 +1011,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125608427</v>
+        <v>125609255</v>
       </c>
       <c r="B5" t="n">
-        <v>75068</v>
+        <v>101801</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>22</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skarptandad daggkåpa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alchemilla oxyodonta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Buser) C. G. Westerl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nymansbodarna, Nymansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>443422</v>
+        <v>443499</v>
       </c>
       <c r="R5" t="n">
-        <v>7022960</v>
+        <v>7023160</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gran i äldre granskog</t>
+          <t>På marken i dikeskant nära före detta fäbod</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 19925-2025 artfynd.xlsx
+++ b/artfynd/A 19925-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -790,7 +790,7 @@
         <v>125607813</v>
       </c>
       <c r="B3" t="n">
-        <v>100525</v>
+        <v>100527</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,45 +899,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125608427</v>
+        <v>125609255</v>
       </c>
       <c r="B4" t="n">
-        <v>75068</v>
+        <v>101803</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>22</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skarptandad daggkåpa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alchemilla oxyodonta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Buser) C. G. Westerl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nymansbodarna, Nymansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443422</v>
+        <v>443499</v>
       </c>
       <c r="R4" t="n">
-        <v>7022960</v>
+        <v>7023160</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gran i äldre granskog</t>
+          <t>På marken i dikeskant nära före detta fäbod</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,54 +1020,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125609255</v>
+        <v>125608427</v>
       </c>
       <c r="B5" t="n">
-        <v>101801</v>
+        <v>75068</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>22</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarptandad daggkåpa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alchemilla oxyodonta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Buser) C. G. Westerl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nymansbodarna, Nymansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>443499</v>
+        <v>443422</v>
       </c>
       <c r="R5" t="n">
-        <v>7023160</v>
+        <v>7022960</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På marken i dikeskant nära före detta fäbod</t>
+          <t>På gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
